--- a/configuration/templates/Fiche d'identité entreprise/1.0/master.xlsx
+++ b/configuration/templates/Fiche d'identité entreprise/1.0/master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mosch\Bureau\KAIVAA\kaivaa-builder\configuration\templates\Fiche d'identité entreprise\1.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139DA905-0ED9-4852-8C77-8009F65358BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB8D9E40-068D-49CD-B6CE-865A3FA8C204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3810" yWindow="3810" windowWidth="21600" windowHeight="11295" activeTab="6" xr2:uid="{1FFF5854-B54B-4C80-B65C-C43C5EF7384C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{1FFF5854-B54B-4C80-B65C-C43C5EF7384C}"/>
   </bookViews>
   <sheets>
     <sheet name="DONNÉES BRUTES" sheetId="26" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -952,6 +952,60 @@
   </cellStyles>
   <dxfs count="29">
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1191,60 +1245,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -20748,29 +20748,29 @@
   <autoFilter ref="A1:AB2" xr:uid="{79E1CCFD-C29F-4239-8558-4F70F8B05FAD}"/>
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{D9C00F17-D0B9-47E9-BDD3-4D9C5C0FDED0}" name="siren"/>
-    <tableColumn id="2" xr3:uid="{72D0A89F-A76F-4AC4-9D3A-4CD3F1A55A5C}" name="date_cloture_exercice" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{72D0A89F-A76F-4AC4-9D3A-4CD3F1A55A5C}" name="date_cloture_exercice" dataDxfId="17"/>
     <tableColumn id="3" xr3:uid="{3EFD615F-AA2D-459F-B4C7-CFFC22318CC1}" name="Chiffre_d_affaires"/>
     <tableColumn id="4" xr3:uid="{80D73410-97C6-4D40-9128-262383E6524C}" name="Marge_brute"/>
     <tableColumn id="5" xr3:uid="{BAD7E762-9FF1-435B-A3F1-352C048EA546}" name="EBE"/>
     <tableColumn id="6" xr3:uid="{3AF3575F-1844-41FF-902F-8EAB8DDD5AD6}" name="EBIT"/>
     <tableColumn id="7" xr3:uid="{C1B7C2D3-EE50-4B20-83E8-6C6C35F45488}" name="Resultat_net"/>
-    <tableColumn id="8" xr3:uid="{1537CC23-C56D-4EB0-B2A3-95305DB00ACE}" name="Taux_d_endettement" dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{536AB2AA-44A8-4F01-8C02-46AFBC6DCAA0}" name="Ratio_de_liquidite" dataDxfId="26"/>
-    <tableColumn id="10" xr3:uid="{FBB19A9A-781C-4896-8A9D-2E1318B24C2B}" name="Ratio_de_vetuste" dataDxfId="25"/>
-    <tableColumn id="11" xr3:uid="{B24A4AA8-9886-4D06-B600-7EC30685FA70}" name="Autonomie_financiere" dataDxfId="24"/>
-    <tableColumn id="12" xr3:uid="{3DB745D5-0419-424E-91C4-B9924D399823}" name="Poids_BFR_exploitation_sur_CA" dataDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{53244D27-3DA2-40CA-8077-20C618624F8D}" name="Couverture_des_interets" dataDxfId="22"/>
-    <tableColumn id="14" xr3:uid="{AB0C9F90-5099-48B9-8487-E86268E4FC91}" name="CAF_sur_CA" dataDxfId="21"/>
-    <tableColumn id="15" xr3:uid="{376D6488-15D4-4F0E-8B09-3E8988FBC4CF}" name="Capacite_de_remboursement" dataDxfId="20"/>
-    <tableColumn id="16" xr3:uid="{D16DFA2E-40D3-4F97-8394-8C21A8C82489}" name="Marge_EBE" dataDxfId="19"/>
-    <tableColumn id="17" xr3:uid="{B1B27CBE-8F94-4970-B010-0C617FFCFEBD}" name="Resultat_courant_avant_impots_sur_CA" dataDxfId="18"/>
-    <tableColumn id="18" xr3:uid="{A7078D23-5164-48BC-A4A8-CFC46C4EAB2D}" name="Poids_BFR_exploitation_sur_CA_jours" dataDxfId="17"/>
-    <tableColumn id="19" xr3:uid="{A23C5DCA-B7DD-4EF2-9126-AED71042D7EC}" name="Rotation_des_stocks_jours" dataDxfId="16"/>
-    <tableColumn id="20" xr3:uid="{367BA43D-2822-4E6B-84EA-9C8D94FFB913}" name="Credit_clients_Jours" dataDxfId="15"/>
-    <tableColumn id="21" xr3:uid="{67FEC185-0EAF-4CAF-A9E3-D005531B61AC}" name="Credit_fournisseurs_Jours" dataDxfId="14"/>
-    <tableColumn id="22" xr3:uid="{AF3E4C10-4D82-4995-9FFA-7E2CE8CB46A2}" name="type_bilan" dataDxfId="13"/>
-    <tableColumn id="23" xr3:uid="{465A446E-7698-4C88-BB95-D9C31EA7A990}" name="confidentiality" dataDxfId="12"/>
-    <tableColumn id="24" xr3:uid="{7E0EE648-DC7A-4C10-AE55-84039A393AD9}" name="Nom_de_l'entreprise" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{1537CC23-C56D-4EB0-B2A3-95305DB00ACE}" name="Taux_d_endettement" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{536AB2AA-44A8-4F01-8C02-46AFBC6DCAA0}" name="Ratio_de_liquidite" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{FBB19A9A-781C-4896-8A9D-2E1318B24C2B}" name="Ratio_de_vetuste" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{B24A4AA8-9886-4D06-B600-7EC30685FA70}" name="Autonomie_financiere" dataDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{3DB745D5-0419-424E-91C4-B9924D399823}" name="Poids_BFR_exploitation_sur_CA" dataDxfId="12"/>
+    <tableColumn id="13" xr3:uid="{53244D27-3DA2-40CA-8077-20C618624F8D}" name="Couverture_des_interets" dataDxfId="11"/>
+    <tableColumn id="14" xr3:uid="{AB0C9F90-5099-48B9-8487-E86268E4FC91}" name="CAF_sur_CA" dataDxfId="10"/>
+    <tableColumn id="15" xr3:uid="{376D6488-15D4-4F0E-8B09-3E8988FBC4CF}" name="Capacite_de_remboursement" dataDxfId="9"/>
+    <tableColumn id="16" xr3:uid="{D16DFA2E-40D3-4F97-8394-8C21A8C82489}" name="Marge_EBE" dataDxfId="8"/>
+    <tableColumn id="17" xr3:uid="{B1B27CBE-8F94-4970-B010-0C617FFCFEBD}" name="Resultat_courant_avant_impots_sur_CA" dataDxfId="7"/>
+    <tableColumn id="18" xr3:uid="{A7078D23-5164-48BC-A4A8-CFC46C4EAB2D}" name="Poids_BFR_exploitation_sur_CA_jours" dataDxfId="6"/>
+    <tableColumn id="19" xr3:uid="{A23C5DCA-B7DD-4EF2-9126-AED71042D7EC}" name="Rotation_des_stocks_jours" dataDxfId="5"/>
+    <tableColumn id="20" xr3:uid="{367BA43D-2822-4E6B-84EA-9C8D94FFB913}" name="Credit_clients_Jours" dataDxfId="4"/>
+    <tableColumn id="21" xr3:uid="{67FEC185-0EAF-4CAF-A9E3-D005531B61AC}" name="Credit_fournisseurs_Jours" dataDxfId="3"/>
+    <tableColumn id="22" xr3:uid="{AF3E4C10-4D82-4995-9FFA-7E2CE8CB46A2}" name="type_bilan" dataDxfId="2"/>
+    <tableColumn id="23" xr3:uid="{465A446E-7698-4C88-BB95-D9C31EA7A990}" name="confidentiality" dataDxfId="1"/>
+    <tableColumn id="24" xr3:uid="{7E0EE648-DC7A-4C10-AE55-84039A393AD9}" name="Nom_de_l'entreprise" dataDxfId="0"/>
     <tableColumn id="27" xr3:uid="{21699414-72C7-4A4E-94EA-765FF08C8A28}" name="Code_NACE"/>
     <tableColumn id="25" xr3:uid="{03B03CBA-639B-4937-9583-2135A393ADA7}" name="Groupes_(NACE3)"/>
     <tableColumn id="26" xr3:uid="{011A9113-0055-4B4B-9BB8-F00CE3094B88}" name="Classe_(NACE4)"/>
@@ -20781,12 +20781,12 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{C89BB5DB-241A-4587-9795-A53E1DD1BE55}" name="Balises" displayName="Balises" ref="C4:E20" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{C89BB5DB-241A-4587-9795-A53E1DD1BE55}" name="Balises" displayName="Balises" ref="C4:E20" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
   <autoFilter ref="C4:E20" xr:uid="{C89BB5DB-241A-4587-9795-A53E1DD1BE55}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{6099FD98-ACB2-4E73-9A6A-2452073B93B5}" name="Balise" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{10252979-8556-4423-8536-262E39599310}" name="Desc" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{38A59B37-8EA6-4A08-B339-21991882C32F}" name="Valeur" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{6099FD98-ACB2-4E73-9A6A-2452073B93B5}" name="Balise" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{10252979-8556-4423-8536-262E39599310}" name="Desc" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{38A59B37-8EA6-4A08-B339-21991882C32F}" name="Valeur" dataDxfId="24">
       <calculatedColumnFormula>s_produit</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -20795,13 +20795,15 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{9D6EACE5-26DB-4F7F-9487-26DB7B53498F}" name="Loop" displayName="Loop" ref="B5:E6" totalsRowShown="0" headerRowDxfId="5" tableBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{9D6EACE5-26DB-4F7F-9487-26DB7B53498F}" name="Loop" displayName="Loop" ref="B5:E6" totalsRowShown="0" headerRowDxfId="23" tableBorderDxfId="22">
   <autoFilter ref="B5:E6" xr:uid="{9D6EACE5-26DB-4F7F-9487-26DB7B53498F}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{57A92AE8-0D79-4270-A771-98B4928EEDE3}" name="ID" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{0153B2F4-CF5A-40D7-B52A-8736C7DFED4F}" name="Itération" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{C2F670A5-B30E-4FDD-A0FC-6BAE9E92844D}" name="Nombre de tests" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{5E26AB54-DDBA-4A1A-B5B5-6BF98CC52480}" name="Résultat" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{57A92AE8-0D79-4270-A771-98B4928EEDE3}" name="ID" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{0153B2F4-CF5A-40D7-B52A-8736C7DFED4F}" name="Itération" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{C2F670A5-B30E-4FDD-A0FC-6BAE9E92844D}" name="Nombre de tests" dataDxfId="19">
+      <calculatedColumnFormula>COUNTA(_xlfn.ANCHORARRAY(Listes!B11))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{5E26AB54-DDBA-4A1A-B5B5-6BF98CC52480}" name="Résultat" dataDxfId="18">
       <calculatedColumnFormula array="1">INDEX(Listes!$C$11:$C$676,Loop[[#This Row],[Itération]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -28050,7 +28052,7 @@
       </c>
       <c r="E20" s="20">
         <f ca="1">TODAY()</f>
-        <v>45939</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="21" spans="3:5" x14ac:dyDescent="0.35">
@@ -28131,7 +28133,8 @@
         <v>1</v>
       </c>
       <c r="D6" s="17">
-        <v>5</v>
+        <f>COUNTA(_xlfn.ANCHORARRAY(Listes!B11))</f>
+        <v>1</v>
       </c>
       <c r="E6" s="15" t="str" cm="1">
         <f t="array" ref="E6">INDEX(Listes!$C$11:$C$676,Loop[[#This Row],[Itération]])</f>
